--- a/src/main/resources/examples/testcases/Master_Test_Cases.xlsx
+++ b/src/main/resources/examples/testcases/Master_Test_Cases.xlsx
@@ -16,7 +16,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1269" uniqueCount="624">
   <si>
-    <t>SDET Assignment A: Test Summary</t>
+    <t>Master Test Cases</t>
   </si>
   <si>
     <t>Selenium + TestNG + Java, Page Object Model on the VOID runtime. Counts below are formulas over the Test Cases sheet.</t>

--- a/src/main/resources/examples/testcases/Master_Test_Cases.xlsx
+++ b/src/main/resources/examples/testcases/Master_Test_Cases.xlsx
@@ -1744,10 +1744,10 @@
     <t>DemoQATest.chk02_childUncheckMakesParentPartial</t>
   </si>
   <si>
-    <t>Assignment requirement coverage</t>
-  </si>
-  <si>
-    <t>Each requirement from the assignment brief and the test cases that cover it.</t>
+    <t>Requirement Coverage</t>
+  </si>
+  <si>
+    <t>Each requirement and the test cases that cover it.</t>
   </si>
   <si>
     <t>Requirement</t>
@@ -1855,7 +1855,7 @@
     <t>CART-08, CART-09, FORM-01</t>
   </si>
   <si>
-    <t>Defects found</t>
+    <t>Defects</t>
   </si>
   <si>
     <t>Each defect is kept as an automated regression anchor: the test asserts today's behavior and will fail when it changes.</t>
